--- a/Data/Building/Corridor.Humidity.xlsx
+++ b/Data/Building/Corridor.Humidity.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709268439</v>
+        <v>1712020576</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709868078</v>
+        <v>1713051308</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709958782</v>
+        <v>1713228093</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1710127259</v>
+        <v>1713328648</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1710464713</v>
+        <v>1713664615</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +638,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1710482677</v>
+        <v>1713835781</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +671,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1710718627</v>
+        <v>1714013764</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +704,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1710812025</v>
+        <v>1714094504</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +737,7 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +756,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1711156237</v>
+        <v>1714283059</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,70 +770,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Corridor</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>1711260776</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Corridor.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Corridor</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>1711599374</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Corridor.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
